--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2810,6 +2810,121 @@
         <v>5948900</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C104" t="n">
+        <v>84.26999664306641</v>
+      </c>
+      <c r="D104" t="n">
+        <v>84.55000305175781</v>
+      </c>
+      <c r="E104" t="n">
+        <v>83.66000366210938</v>
+      </c>
+      <c r="F104" t="n">
+        <v>84.01000213623047</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4816900</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C105" t="n">
+        <v>84.41999816894531</v>
+      </c>
+      <c r="D105" t="n">
+        <v>84.91000366210938</v>
+      </c>
+      <c r="E105" t="n">
+        <v>84.23999786376953</v>
+      </c>
+      <c r="F105" t="n">
+        <v>84.87000274658203</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5892000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C106" t="n">
+        <v>83.58999633789062</v>
+      </c>
+      <c r="D106" t="n">
+        <v>83.88999938964844</v>
+      </c>
+      <c r="E106" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="F106" t="n">
+        <v>83.68000030517578</v>
+      </c>
+      <c r="G106" t="n">
+        <v>9057300</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C107" t="n">
+        <v>84.27999877929688</v>
+      </c>
+      <c r="D107" t="n">
+        <v>84.91999816894531</v>
+      </c>
+      <c r="E107" t="n">
+        <v>83.83000183105469</v>
+      </c>
+      <c r="F107" t="n">
+        <v>84.72000122070312</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3051300</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C108" t="n">
+        <v>81.22000122070312</v>
+      </c>
+      <c r="D108" t="n">
+        <v>82.93499755859375</v>
+      </c>
+      <c r="E108" t="n">
+        <v>81.15000152587891</v>
+      </c>
+      <c r="F108" t="n">
+        <v>82.87000274658203</v>
+      </c>
+      <c r="G108" t="n">
+        <v>7769766</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,7 +2913,7 @@
         <v>81.22000122070312</v>
       </c>
       <c r="D108" t="n">
-        <v>82.93499755859375</v>
+        <v>82.94000244140625</v>
       </c>
       <c r="E108" t="n">
         <v>81.15000152587891</v>
@@ -2922,7 +2922,53 @@
         <v>82.87000274658203</v>
       </c>
       <c r="G108" t="n">
-        <v>7769766</v>
+        <v>7787500</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C109" t="n">
+        <v>81.37999725341797</v>
+      </c>
+      <c r="D109" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="E109" t="n">
+        <v>81.15000152587891</v>
+      </c>
+      <c r="F109" t="n">
+        <v>81.45999908447266</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6513400</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C110" t="n">
+        <v>80.08000183105469</v>
+      </c>
+      <c r="D110" t="n">
+        <v>82.06199645996094</v>
+      </c>
+      <c r="E110" t="n">
+        <v>79.68000030517578</v>
+      </c>
+      <c r="F110" t="n">
+        <v>81.45999908447266</v>
+      </c>
+      <c r="G110" t="n">
+        <v>8394231</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -2968,7 +2968,7 @@
         <v>81.45999908447266</v>
       </c>
       <c r="G110" t="n">
-        <v>8394231</v>
+        <v>8711843</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -2956,7 +2956,7 @@
         <v>46182</v>
       </c>
       <c r="C110" t="n">
-        <v>80.08000183105469</v>
+        <v>80.06999969482422</v>
       </c>
       <c r="D110" t="n">
         <v>82.06199645996094</v>
@@ -2968,7 +2968,7 @@
         <v>81.45999908447266</v>
       </c>
       <c r="G110" t="n">
-        <v>8711843</v>
+        <v>9146765</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -2968,7 +2968,7 @@
         <v>81.45999908447266</v>
       </c>
       <c r="G110" t="n">
-        <v>9146765</v>
+        <v>9167213</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2959,7 +2959,7 @@
         <v>80.06999969482422</v>
       </c>
       <c r="D110" t="n">
-        <v>82.06199645996094</v>
+        <v>82.05999755859375</v>
       </c>
       <c r="E110" t="n">
         <v>79.68000030517578</v>
@@ -2968,7 +2968,76 @@
         <v>81.45999908447266</v>
       </c>
       <c r="G110" t="n">
-        <v>9167213</v>
+        <v>9210000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C111" t="n">
+        <v>76.79000091552734</v>
+      </c>
+      <c r="D111" t="n">
+        <v>78.73000335693359</v>
+      </c>
+      <c r="E111" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="F111" t="n">
+        <v>78.01999664306641</v>
+      </c>
+      <c r="G111" t="n">
+        <v>11399900</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C112" t="n">
+        <v>79.12999725341797</v>
+      </c>
+      <c r="D112" t="n">
+        <v>79.33999633789062</v>
+      </c>
+      <c r="E112" t="n">
+        <v>76.20999908447266</v>
+      </c>
+      <c r="F112" t="n">
+        <v>76.62000274658203</v>
+      </c>
+      <c r="G112" t="n">
+        <v>13527200</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C113" t="n">
+        <v>79.19000244140625</v>
+      </c>
+      <c r="D113" t="n">
+        <v>79.66000366210938</v>
+      </c>
+      <c r="E113" t="n">
+        <v>78.56999969482422</v>
+      </c>
+      <c r="F113" t="n">
+        <v>79.05000305175781</v>
+      </c>
+      <c r="G113" t="n">
+        <v>9870500</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,7 +3037,122 @@
         <v>79.05000305175781</v>
       </c>
       <c r="G113" t="n">
-        <v>9870500</v>
+        <v>9878300</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C114" t="n">
+        <v>81.26000213623047</v>
+      </c>
+      <c r="D114" t="n">
+        <v>82.18000030517578</v>
+      </c>
+      <c r="E114" t="n">
+        <v>81.18000030517578</v>
+      </c>
+      <c r="F114" t="n">
+        <v>81.88999938964844</v>
+      </c>
+      <c r="G114" t="n">
+        <v>5130600</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C115" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D115" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="E115" t="n">
+        <v>81.12000274658203</v>
+      </c>
+      <c r="F115" t="n">
+        <v>81.51999664306641</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3922100</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C116" t="n">
+        <v>79.63999938964844</v>
+      </c>
+      <c r="D116" t="n">
+        <v>82.40000152587891</v>
+      </c>
+      <c r="E116" t="n">
+        <v>79.33000183105469</v>
+      </c>
+      <c r="F116" t="n">
+        <v>81.52999877929688</v>
+      </c>
+      <c r="G116" t="n">
+        <v>14275600</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C117" t="n">
+        <v>79.33000183105469</v>
+      </c>
+      <c r="D117" t="n">
+        <v>80.44000244140625</v>
+      </c>
+      <c r="E117" t="n">
+        <v>79.02999877929688</v>
+      </c>
+      <c r="F117" t="n">
+        <v>80.19999694824219</v>
+      </c>
+      <c r="G117" t="n">
+        <v>8405500</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C118" t="n">
+        <v>78.80000305175781</v>
+      </c>
+      <c r="D118" t="n">
+        <v>79.18019866943359</v>
+      </c>
+      <c r="E118" t="n">
+        <v>78.41999816894531</v>
+      </c>
+      <c r="F118" t="n">
+        <v>78.74500274658203</v>
+      </c>
+      <c r="G118" t="n">
+        <v>9650848</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -3152,7 +3152,7 @@
         <v>78.74500274658203</v>
       </c>
       <c r="G118" t="n">
-        <v>9650848</v>
+        <v>9660709</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,16 +3143,223 @@
         <v>78.80000305175781</v>
       </c>
       <c r="D118" t="n">
-        <v>79.18019866943359</v>
+        <v>79.18000030517578</v>
       </c>
       <c r="E118" t="n">
         <v>78.41999816894531</v>
       </c>
       <c r="F118" t="n">
-        <v>78.74500274658203</v>
+        <v>78.75</v>
       </c>
       <c r="G118" t="n">
-        <v>9660709</v>
+        <v>9674400</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C119" t="n">
+        <v>77.33000183105469</v>
+      </c>
+      <c r="D119" t="n">
+        <v>77.94000244140625</v>
+      </c>
+      <c r="E119" t="n">
+        <v>77.29000091552734</v>
+      </c>
+      <c r="F119" t="n">
+        <v>77.40000152587891</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4652100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C120" t="n">
+        <v>74.98999786376953</v>
+      </c>
+      <c r="D120" t="n">
+        <v>76.01000213623047</v>
+      </c>
+      <c r="E120" t="n">
+        <v>74.44000244140625</v>
+      </c>
+      <c r="F120" t="n">
+        <v>74.77999877929688</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10609200</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C121" t="n">
+        <v>75.70999908447266</v>
+      </c>
+      <c r="D121" t="n">
+        <v>76.04000091552734</v>
+      </c>
+      <c r="E121" t="n">
+        <v>75.18000030517578</v>
+      </c>
+      <c r="F121" t="n">
+        <v>75.62999725341797</v>
+      </c>
+      <c r="G121" t="n">
+        <v>6287200</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C122" t="n">
+        <v>76.55999755859375</v>
+      </c>
+      <c r="D122" t="n">
+        <v>77.01999664306641</v>
+      </c>
+      <c r="E122" t="n">
+        <v>76.06999969482422</v>
+      </c>
+      <c r="F122" t="n">
+        <v>76.29000091552734</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4671800</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C123" t="n">
+        <v>75.52999877929688</v>
+      </c>
+      <c r="D123" t="n">
+        <v>76.05000305175781</v>
+      </c>
+      <c r="E123" t="n">
+        <v>75.20999908447266</v>
+      </c>
+      <c r="F123" t="n">
+        <v>75.95999908447266</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4262200</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>75.51000213623047</v>
+      </c>
+      <c r="D124" t="n">
+        <v>76.41000366210938</v>
+      </c>
+      <c r="E124" t="n">
+        <v>75.45999908447266</v>
+      </c>
+      <c r="F124" t="n">
+        <v>75.66000366210938</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5512900</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C125" t="n">
+        <v>75.95999908447266</v>
+      </c>
+      <c r="D125" t="n">
+        <v>77.41000366210938</v>
+      </c>
+      <c r="E125" t="n">
+        <v>75.87999725341797</v>
+      </c>
+      <c r="F125" t="n">
+        <v>76.08999633789062</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6798100</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C126" t="n">
+        <v>77.51000213623047</v>
+      </c>
+      <c r="D126" t="n">
+        <v>77.93000030517578</v>
+      </c>
+      <c r="E126" t="n">
+        <v>77.12000274658203</v>
+      </c>
+      <c r="F126" t="n">
+        <v>77.31999969482422</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4674000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C127" t="n">
+        <v>78.30000305175781</v>
+      </c>
+      <c r="D127" t="n">
+        <v>78.38500213623047</v>
+      </c>
+      <c r="E127" t="n">
+        <v>77.64029693603516</v>
+      </c>
+      <c r="F127" t="n">
+        <v>77.90000152587891</v>
+      </c>
+      <c r="G127" t="n">
+        <v>8362701</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3350,16 +3350,108 @@
         <v>78.30000305175781</v>
       </c>
       <c r="D127" t="n">
-        <v>78.38500213623047</v>
+        <v>78.38999938964844</v>
       </c>
       <c r="E127" t="n">
-        <v>77.64029693603516</v>
+        <v>77.63999938964844</v>
       </c>
       <c r="F127" t="n">
         <v>77.90000152587891</v>
       </c>
       <c r="G127" t="n">
-        <v>8362701</v>
+        <v>11490500</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C128" t="n">
+        <v>77.37000274658203</v>
+      </c>
+      <c r="D128" t="n">
+        <v>78.61000061035156</v>
+      </c>
+      <c r="E128" t="n">
+        <v>76.97000122070312</v>
+      </c>
+      <c r="F128" t="n">
+        <v>78.34999847412109</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3420700</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C129" t="n">
+        <v>76.73999786376953</v>
+      </c>
+      <c r="D129" t="n">
+        <v>76.94000244140625</v>
+      </c>
+      <c r="E129" t="n">
+        <v>75.62999725341797</v>
+      </c>
+      <c r="F129" t="n">
+        <v>76.48999786376953</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3337100</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C130" t="n">
+        <v>77.51000213623047</v>
+      </c>
+      <c r="D130" t="n">
+        <v>77.80000305175781</v>
+      </c>
+      <c r="E130" t="n">
+        <v>77.36000061035156</v>
+      </c>
+      <c r="F130" t="n">
+        <v>77.58000183105469</v>
+      </c>
+      <c r="G130" t="n">
+        <v>5457000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C131" t="n">
+        <v>77.26000213623047</v>
+      </c>
+      <c r="D131" t="n">
+        <v>77.38999938964844</v>
+      </c>
+      <c r="E131" t="n">
+        <v>76.58999633789062</v>
+      </c>
+      <c r="F131" t="n">
+        <v>76.86000061035156</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2748000</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3451,7 +3451,122 @@
         <v>76.86000061035156</v>
       </c>
       <c r="G131" t="n">
-        <v>2748000</v>
+        <v>2748600</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C132" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="D132" t="n">
+        <v>76.41999816894531</v>
+      </c>
+      <c r="E132" t="n">
+        <v>74.97000122070312</v>
+      </c>
+      <c r="F132" t="n">
+        <v>76.38999938964844</v>
+      </c>
+      <c r="G132" t="n">
+        <v>4392400</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C133" t="n">
+        <v>76.26999664306641</v>
+      </c>
+      <c r="D133" t="n">
+        <v>77.11000061035156</v>
+      </c>
+      <c r="E133" t="n">
+        <v>76.02999877929688</v>
+      </c>
+      <c r="F133" t="n">
+        <v>76.76999664306641</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3520800</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C134" t="n">
+        <v>76.27999877929688</v>
+      </c>
+      <c r="D134" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="E134" t="n">
+        <v>75.73000335693359</v>
+      </c>
+      <c r="F134" t="n">
+        <v>76.26000213623047</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2942300</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C135" t="n">
+        <v>74.80000305175781</v>
+      </c>
+      <c r="D135" t="n">
+        <v>75.51000213623047</v>
+      </c>
+      <c r="E135" t="n">
+        <v>74.62000274658203</v>
+      </c>
+      <c r="F135" t="n">
+        <v>75.30000305175781</v>
+      </c>
+      <c r="G135" t="n">
+        <v>5619200</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C136" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="D136" t="n">
+        <v>75.65000152587891</v>
+      </c>
+      <c r="E136" t="n">
+        <v>74.55000305175781</v>
+      </c>
+      <c r="F136" t="n">
+        <v>74.59999847412109</v>
+      </c>
+      <c r="G136" t="n">
+        <v>6287000</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,191 @@
         <v>74.59999847412109</v>
       </c>
       <c r="G136" t="n">
-        <v>6287000</v>
+        <v>6288100</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C137" t="n">
+        <v>75.34999847412109</v>
+      </c>
+      <c r="D137" t="n">
+        <v>75.58000183105469</v>
+      </c>
+      <c r="E137" t="n">
+        <v>75.18000030517578</v>
+      </c>
+      <c r="F137" t="n">
+        <v>75.37000274658203</v>
+      </c>
+      <c r="G137" t="n">
+        <v>7583800</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C138" t="n">
+        <v>76.81999969482422</v>
+      </c>
+      <c r="D138" t="n">
+        <v>76.84999847412109</v>
+      </c>
+      <c r="E138" t="n">
+        <v>76.05999755859375</v>
+      </c>
+      <c r="F138" t="n">
+        <v>76.16999816894531</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3570000</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C139" t="n">
+        <v>77.69000244140625</v>
+      </c>
+      <c r="D139" t="n">
+        <v>78.33000183105469</v>
+      </c>
+      <c r="E139" t="n">
+        <v>77.62999725341797</v>
+      </c>
+      <c r="F139" t="n">
+        <v>77.72000122070312</v>
+      </c>
+      <c r="G139" t="n">
+        <v>7764900</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C140" t="n">
+        <v>76.15000152587891</v>
+      </c>
+      <c r="D140" t="n">
+        <v>76.45999908447266</v>
+      </c>
+      <c r="E140" t="n">
+        <v>75.94999694824219</v>
+      </c>
+      <c r="F140" t="n">
+        <v>76.29000091552734</v>
+      </c>
+      <c r="G140" t="n">
+        <v>4105300</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C141" t="n">
+        <v>76.23000335693359</v>
+      </c>
+      <c r="D141" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="E141" t="n">
+        <v>76.06999969482422</v>
+      </c>
+      <c r="F141" t="n">
+        <v>76.08999633789062</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2593500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C142" t="n">
+        <v>76.77999877929688</v>
+      </c>
+      <c r="D142" t="n">
+        <v>76.98000335693359</v>
+      </c>
+      <c r="E142" t="n">
+        <v>76.44000244140625</v>
+      </c>
+      <c r="F142" t="n">
+        <v>76.63999938964844</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2335300</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C143" t="n">
+        <v>75.69999694824219</v>
+      </c>
+      <c r="D143" t="n">
+        <v>76.08999633789062</v>
+      </c>
+      <c r="E143" t="n">
+        <v>75.44000244140625</v>
+      </c>
+      <c r="F143" t="n">
+        <v>75.76000213623047</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4775200</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C144" t="n">
+        <v>76.04000091552734</v>
+      </c>
+      <c r="D144" t="n">
+        <v>77.38999938964844</v>
+      </c>
+      <c r="E144" t="n">
+        <v>75.12999725341797</v>
+      </c>
+      <c r="F144" t="n">
+        <v>75.48000335693359</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4180795</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3750,7 +3750,145 @@
         <v>75.48000335693359</v>
       </c>
       <c r="G144" t="n">
-        <v>4180795</v>
+        <v>4203200</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C145" t="n">
+        <v>77.30000305175781</v>
+      </c>
+      <c r="D145" t="n">
+        <v>77.44999694824219</v>
+      </c>
+      <c r="E145" t="n">
+        <v>76.61000061035156</v>
+      </c>
+      <c r="F145" t="n">
+        <v>76.69000244140625</v>
+      </c>
+      <c r="G145" t="n">
+        <v>3534200</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C146" t="n">
+        <v>76.16999816894531</v>
+      </c>
+      <c r="D146" t="n">
+        <v>76.26000213623047</v>
+      </c>
+      <c r="E146" t="n">
+        <v>75.59999847412109</v>
+      </c>
+      <c r="F146" t="n">
+        <v>76.01000213623047</v>
+      </c>
+      <c r="G146" t="n">
+        <v>5262600</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C147" t="n">
+        <v>76.19000244140625</v>
+      </c>
+      <c r="D147" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="E147" t="n">
+        <v>75.56999969482422</v>
+      </c>
+      <c r="F147" t="n">
+        <v>75.84999847412109</v>
+      </c>
+      <c r="G147" t="n">
+        <v>4316600</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C148" t="n">
+        <v>76.69000244140625</v>
+      </c>
+      <c r="D148" t="n">
+        <v>77.19000244140625</v>
+      </c>
+      <c r="E148" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F148" t="n">
+        <v>76.66999816894531</v>
+      </c>
+      <c r="G148" t="n">
+        <v>10095400</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C149" t="n">
+        <v>79.84999847412109</v>
+      </c>
+      <c r="D149" t="n">
+        <v>80.23999786376953</v>
+      </c>
+      <c r="E149" t="n">
+        <v>78.76999664306641</v>
+      </c>
+      <c r="F149" t="n">
+        <v>78.93000030517578</v>
+      </c>
+      <c r="G149" t="n">
+        <v>11119200</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C150" t="n">
+        <v>79.87000274658203</v>
+      </c>
+      <c r="D150" t="n">
+        <v>80.36620330810547</v>
+      </c>
+      <c r="E150" t="n">
+        <v>79.39029693603516</v>
+      </c>
+      <c r="F150" t="n">
+        <v>79.84999847412109</v>
+      </c>
+      <c r="G150" t="n">
+        <v>7226011</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3879,16 +3879,154 @@
         <v>79.87000274658203</v>
       </c>
       <c r="D150" t="n">
-        <v>80.36620330810547</v>
+        <v>80.37000274658203</v>
       </c>
       <c r="E150" t="n">
-        <v>79.39029693603516</v>
+        <v>79.38999938964844</v>
       </c>
       <c r="F150" t="n">
         <v>79.84999847412109</v>
       </c>
       <c r="G150" t="n">
-        <v>7226011</v>
+        <v>7368800</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C151" t="n">
+        <v>81.68000030517578</v>
+      </c>
+      <c r="D151" t="n">
+        <v>82.11000061035156</v>
+      </c>
+      <c r="E151" t="n">
+        <v>81.37000274658203</v>
+      </c>
+      <c r="F151" t="n">
+        <v>81.91999816894531</v>
+      </c>
+      <c r="G151" t="n">
+        <v>8402700</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C152" t="n">
+        <v>82.51000213623047</v>
+      </c>
+      <c r="D152" t="n">
+        <v>82.65000152587891</v>
+      </c>
+      <c r="E152" t="n">
+        <v>81.15000152587891</v>
+      </c>
+      <c r="F152" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3559900</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C153" t="n">
+        <v>82.18000030517578</v>
+      </c>
+      <c r="D153" t="n">
+        <v>82.80999755859375</v>
+      </c>
+      <c r="E153" t="n">
+        <v>81.97000122070312</v>
+      </c>
+      <c r="F153" t="n">
+        <v>82.68000030517578</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3718200</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C154" t="n">
+        <v>82.98000335693359</v>
+      </c>
+      <c r="D154" t="n">
+        <v>83.45999908447266</v>
+      </c>
+      <c r="E154" t="n">
+        <v>82.65000152587891</v>
+      </c>
+      <c r="F154" t="n">
+        <v>83.05999755859375</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4824700</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C155" t="n">
+        <v>81.77999877929688</v>
+      </c>
+      <c r="D155" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E155" t="n">
+        <v>81.65000152587891</v>
+      </c>
+      <c r="F155" t="n">
+        <v>82.41000366210938</v>
+      </c>
+      <c r="G155" t="n">
+        <v>4245100</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C156" t="n">
+        <v>82.27999877929688</v>
+      </c>
+      <c r="D156" t="n">
+        <v>82.66000366210938</v>
+      </c>
+      <c r="E156" t="n">
+        <v>82.18949890136719</v>
+      </c>
+      <c r="F156" t="n">
+        <v>82.41999816894531</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2108039</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4020,13 +4020,59 @@
         <v>82.66000366210938</v>
       </c>
       <c r="E156" t="n">
-        <v>82.18949890136719</v>
+        <v>82.19000244140625</v>
       </c>
       <c r="F156" t="n">
         <v>82.41999816894531</v>
       </c>
       <c r="G156" t="n">
-        <v>2108039</v>
+        <v>2145200</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C157" t="n">
+        <v>83.11000061035156</v>
+      </c>
+      <c r="D157" t="n">
+        <v>83.26999664306641</v>
+      </c>
+      <c r="E157" t="n">
+        <v>82.44000244140625</v>
+      </c>
+      <c r="F157" t="n">
+        <v>82.48000335693359</v>
+      </c>
+      <c r="G157" t="n">
+        <v>4936100</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C158" t="n">
+        <v>81.70999908447266</v>
+      </c>
+      <c r="D158" t="n">
+        <v>82.87000274658203</v>
+      </c>
+      <c r="E158" t="n">
+        <v>81.56999969482422</v>
+      </c>
+      <c r="F158" t="n">
+        <v>82.51000213623047</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3100657</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4072,7 +4072,30 @@
         <v>82.51000213623047</v>
       </c>
       <c r="G158" t="n">
-        <v>3100657</v>
+        <v>3153200</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C159" t="n">
+        <v>84.75499725341797</v>
+      </c>
+      <c r="D159" t="n">
+        <v>84.81500244140625</v>
+      </c>
+      <c r="E159" t="n">
+        <v>83.52279663085938</v>
+      </c>
+      <c r="F159" t="n">
+        <v>83.80999755859375</v>
+      </c>
+      <c r="G159" t="n">
+        <v>9839943</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4083,19 +4083,157 @@
         <v>46253</v>
       </c>
       <c r="C159" t="n">
-        <v>84.75499725341797</v>
+        <v>84.83999633789062</v>
       </c>
       <c r="D159" t="n">
-        <v>84.81500244140625</v>
+        <v>84.84999847412109</v>
       </c>
       <c r="E159" t="n">
-        <v>83.52279663085938</v>
+        <v>83.51999664306641</v>
       </c>
       <c r="F159" t="n">
         <v>83.80999755859375</v>
       </c>
       <c r="G159" t="n">
-        <v>9839943</v>
+        <v>10875400</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C160" t="n">
+        <v>85.12999725341797</v>
+      </c>
+      <c r="D160" t="n">
+        <v>85.36000061035156</v>
+      </c>
+      <c r="E160" t="n">
+        <v>84.01000213623047</v>
+      </c>
+      <c r="F160" t="n">
+        <v>84.08000183105469</v>
+      </c>
+      <c r="G160" t="n">
+        <v>9100300</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C161" t="n">
+        <v>86.79000091552734</v>
+      </c>
+      <c r="D161" t="n">
+        <v>87.08999633789062</v>
+      </c>
+      <c r="E161" t="n">
+        <v>85.98999786376953</v>
+      </c>
+      <c r="F161" t="n">
+        <v>86.19000244140625</v>
+      </c>
+      <c r="G161" t="n">
+        <v>6293800</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C162" t="n">
+        <v>87.47000122070312</v>
+      </c>
+      <c r="D162" t="n">
+        <v>88.01999664306641</v>
+      </c>
+      <c r="E162" t="n">
+        <v>86.94999694824219</v>
+      </c>
+      <c r="F162" t="n">
+        <v>87.86000061035156</v>
+      </c>
+      <c r="G162" t="n">
+        <v>6764400</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C163" t="n">
+        <v>87.76000213623047</v>
+      </c>
+      <c r="D163" t="n">
+        <v>87.76000213623047</v>
+      </c>
+      <c r="E163" t="n">
+        <v>86.56999969482422</v>
+      </c>
+      <c r="F163" t="n">
+        <v>86.66999816894531</v>
+      </c>
+      <c r="G163" t="n">
+        <v>4523700</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C164" t="n">
+        <v>86.37000274658203</v>
+      </c>
+      <c r="D164" t="n">
+        <v>87.09999847412109</v>
+      </c>
+      <c r="E164" t="n">
+        <v>86.16000366210938</v>
+      </c>
+      <c r="F164" t="n">
+        <v>86.68000030517578</v>
+      </c>
+      <c r="G164" t="n">
+        <v>4005200</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C165" t="n">
+        <v>86.62000274658203</v>
+      </c>
+      <c r="D165" t="n">
+        <v>86.78500366210938</v>
+      </c>
+      <c r="E165" t="n">
+        <v>85.76999664306641</v>
+      </c>
+      <c r="F165" t="n">
+        <v>86.27999877929688</v>
+      </c>
+      <c r="G165" t="n">
+        <v>4235603</v>
       </c>
     </row>
   </sheetData>

--- a/Data/iau.xlsx
+++ b/Data/iau.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4224,7 +4224,7 @@
         <v>86.62000274658203</v>
       </c>
       <c r="D165" t="n">
-        <v>86.78500366210938</v>
+        <v>86.79000091552734</v>
       </c>
       <c r="E165" t="n">
         <v>85.76999664306641</v>
@@ -4233,7 +4233,76 @@
         <v>86.27999877929688</v>
       </c>
       <c r="G165" t="n">
-        <v>4235603</v>
+        <v>4257700</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C166" t="n">
+        <v>83.81999969482422</v>
+      </c>
+      <c r="D166" t="n">
+        <v>87.06999969482422</v>
+      </c>
+      <c r="E166" t="n">
+        <v>83.56999969482422</v>
+      </c>
+      <c r="F166" t="n">
+        <v>86.55000305175781</v>
+      </c>
+      <c r="G166" t="n">
+        <v>9443100</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C167" t="n">
+        <v>83.70999908447266</v>
+      </c>
+      <c r="D167" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="E167" t="n">
+        <v>83.01000213623047</v>
+      </c>
+      <c r="F167" t="n">
+        <v>83.56999969482422</v>
+      </c>
+      <c r="G167" t="n">
+        <v>3407600</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C168" t="n">
+        <v>81.34999847412109</v>
+      </c>
+      <c r="D168" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="E168" t="n">
+        <v>81.26999664306641</v>
+      </c>
+      <c r="F168" t="n">
+        <v>81.65000152587891</v>
+      </c>
+      <c r="G168" t="n">
+        <v>4807095</v>
       </c>
     </row>
   </sheetData>
